--- a/Employee_Reports_wi48/Nishan Ekanayake Ekanayake Mudiyanselage Q0574.xlsx
+++ b/Employee_Reports_wi48/Nishan Ekanayake Ekanayake Mudiyanselage Q0574.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1350,11 +1350,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1399,11 +1399,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1448,11 +1448,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1485,11 +1485,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-350</v>
+        <v>-353</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1522,11 +1522,11 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-73</v>
+        <v>-76</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1545,9 +1545,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
           <t>29-Jan-2026</t>
@@ -1559,11 +1571,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1608,11 +1620,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1645,11 +1657,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1682,11 +1694,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1719,11 +1731,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1768,11 +1780,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1805,11 +1817,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -2298,7 +2310,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7945</v>
+        <v>7942</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2321,7 +2333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2393,7 +2405,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7933</v>
+        <v>7930</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2422,7 +2434,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7933</v>
+        <v>7930</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2451,7 +2463,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7936</v>
+        <v>7933</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2480,7 +2492,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2509,7 +2521,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2538,7 +2550,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7936</v>
+        <v>7933</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2567,7 +2579,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2596,7 +2608,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2625,7 +2637,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7979</v>
+        <v>7976</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2654,7 +2666,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2674,16 +2686,16 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>19-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7981</v>
+        <v>7991</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2703,16 +2715,16 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>19-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7981</v>
+        <v>7991</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2732,16 +2744,16 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>19-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7981</v>
+        <v>7991</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2761,16 +2773,16 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>19-May-2048</t>
+          <t>01-Jun-2048</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7981</v>
+        <v>7991</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2799,7 +2811,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7979</v>
+        <v>7976</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2828,7 +2840,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7979</v>
+        <v>7976</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2857,7 +2869,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7979</v>
+        <v>7976</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2886,7 +2898,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7979</v>
+        <v>7976</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2894,6 +2906,35 @@
         </is>
       </c>
       <c r="G20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>floor scale</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>07-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>01-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>7991</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
